--- a/Attendance Roster_Splunk Basics_11-12 May_VILT29624.xlsx
+++ b/Attendance Roster_Splunk Basics_11-12 May_VILT29624.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_IN_SPLK_11_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78630B29-364A-4203-BEF3-47AA62CA3D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BFE2E-E0BF-4A09-9762-B8D1BD9E447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
   <si>
     <t>Start Date</t>
   </si>
@@ -124,9 +124,6 @@
     <t>Anviksha Dixit</t>
   </si>
   <si>
-    <t>26MMS0141_TR</t>
-  </si>
-  <si>
     <t>siLv3rfoX%35%</t>
   </si>
   <si>
@@ -170,6 +167,13 @@
   </si>
   <si>
     <t>Cloud Lab URL as follows :  https://cloud.cdp.rpsconsulting.in/console/</t>
+  </si>
+  <si>
+    <t>Windows Credentials: username: Admin 
+Password: 15blacK#321#</t>
+  </si>
+  <si>
+    <t>26MMS0141_U12</t>
   </si>
 </sst>
 </file>
@@ -566,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -634,24 +638,30 @@
     <xf numFmtId="15" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -944,10 +954,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="26"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1179,7 +1189,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88676AFF-1C37-4D18-940C-CD45BDA833B9}">
-  <dimension ref="B3:E23"/>
+  <dimension ref="B3:L23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="62.33203125" bestFit="1" customWidth="1"/>
@@ -1188,122 +1198,139 @@
     <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="30" t="s">
+      <c r="D11" s="28" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E11" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+    </row>
+    <row r="12" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D12" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+    </row>
+    <row r="13" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D13" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D14" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D15" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="30" t="s">
-        <v>33</v>
+      <c r="D16" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1313,11 +1340,11 @@
       <c r="C17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>33</v>
+      <c r="D17" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1327,11 +1354,11 @@
       <c r="C18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>33</v>
+      <c r="D18" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1341,11 +1368,11 @@
       <c r="C19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>33</v>
+      <c r="D19" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1355,11 +1382,11 @@
       <c r="C20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>33</v>
+      <c r="D20" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1369,28 +1396,29 @@
       <c r="C21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>33</v>
+      <c r="D21" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
     </row>
     <row r="23" spans="2:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B3:E3"/>
+    <mergeCell ref="H10:L12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" tooltip="https://cloud.cdp.rpsconsulting.in/console/" display="https://cloud.cdp.rpsconsulting.in/console/" xr:uid="{988D2341-7E30-4C4A-8F84-9C23CF679FAB}"/>

--- a/Attendance Roster_Splunk Basics_11-12 May_VILT29624.xlsx
+++ b/Attendance Roster_Splunk Basics_11-12 May_VILT29624.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\CISCO_IN_SPLK_11_05_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BFE2E-E0BF-4A09-9762-B8D1BD9E447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBF8AED-390B-4168-BFE5-C4F39E530DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="50">
   <si>
     <t>Start Date</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>26MMS0141_U12</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -651,17 +654,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -954,10 +957,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="31"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1044,7 +1047,9 @@
       <c r="C12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="12"/>
+      <c r="D12" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
@@ -1054,7 +1059,9 @@
       <c r="C13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="15"/>
+      <c r="D13" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
@@ -1066,7 +1073,9 @@
       <c r="C14" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
@@ -1078,7 +1087,9 @@
       <c r="C15" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="15"/>
+      <c r="D15" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -1090,7 +1101,9 @@
       <c r="C16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="15"/>
+      <c r="D16" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
@@ -1102,7 +1115,9 @@
       <c r="C17" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="15"/>
+      <c r="D17" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
@@ -1114,7 +1129,9 @@
       <c r="C18" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="15"/>
+      <c r="D18" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
@@ -1126,7 +1143,9 @@
       <c r="C19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="15"/>
+      <c r="D19" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
@@ -1138,7 +1157,9 @@
       <c r="C20" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="15"/>
+      <c r="D20" s="15" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
@@ -1150,7 +1171,9 @@
       <c r="C21" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="15"/>
+      <c r="D21" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
@@ -1162,7 +1185,9 @@
       <c r="C22" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="17"/>
+      <c r="D22" s="17" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18" t="s">
@@ -1174,7 +1199,9 @@
       <c r="C23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="20"/>
+      <c r="D23" s="20" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1233,13 +1260,13 @@
       <c r="E10" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="11" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
@@ -1252,11 +1279,11 @@
       <c r="E11" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
     </row>
     <row r="12" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
@@ -1271,11 +1298,11 @@
       <c r="E12" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
     </row>
     <row r="13" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
